--- a/quant_apostas_elite_novo.xlsx
+++ b/quant_apostas_elite_novo.xlsx
@@ -35,7 +35,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -46,6 +46,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="000D1B2A"/>
         <bgColor rgb="000D1B2A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D4EDDA"/>
+        <bgColor rgb="00D4EDDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8D7DA"/>
+        <bgColor rgb="00F8D7DA"/>
       </patternFill>
     </fill>
   </fills>
@@ -81,7 +93,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -90,6 +102,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -457,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M57"/>
+  <dimension ref="A1:M60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1135,15 +1153,15 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>1-5</t>
         </is>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" s="3" t="inlineStr">
-        <is>
-          <t>PENDENTE</t>
+        <v>1.42</v>
+      </c>
+      <c r="M12" s="4" t="inlineStr">
+        <is>
+          <t>GANHO</t>
         </is>
       </c>
     </row>
@@ -1190,15 +1208,15 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>5-2</t>
         </is>
       </c>
       <c r="L13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="3" t="inlineStr">
-        <is>
-          <t>PENDENTE</t>
+        <v>1.16</v>
+      </c>
+      <c r="M13" s="4" t="inlineStr">
+        <is>
+          <t>GANHO</t>
         </is>
       </c>
     </row>
@@ -1245,15 +1263,15 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="L14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3" t="inlineStr">
-        <is>
-          <t>PENDENTE</t>
+        <v>-1</v>
+      </c>
+      <c r="M14" s="5" t="inlineStr">
+        <is>
+          <t>PERDIDO</t>
         </is>
       </c>
     </row>
@@ -1630,15 +1648,15 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="L21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" s="3" t="inlineStr">
-        <is>
-          <t>PENDENTE</t>
+        <v>-1.14</v>
+      </c>
+      <c r="M21" s="5" t="inlineStr">
+        <is>
+          <t>PERDIDO</t>
         </is>
       </c>
     </row>
@@ -2180,15 +2198,15 @@
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" s="3" t="inlineStr">
-        <is>
-          <t>PENDENTE</t>
+        <v>1.31</v>
+      </c>
+      <c r="M31" s="4" t="inlineStr">
+        <is>
+          <t>GANHO</t>
         </is>
       </c>
     </row>
@@ -3617,6 +3635,171 @@
         <v>0</v>
       </c>
       <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>06/11/2026 20:00</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>Everton FC vs Coventry City FC</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>61.90729122376535</v>
+      </c>
+      <c r="G58" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H58" s="3" t="n">
+        <v>-0.1333</v>
+      </c>
+      <c r="I58" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>Est. 9 cantos</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>06/11/2026 19:45</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>FL1</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>Toulouse FC vs RC Strasbourg Alsace</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>85.94112717767014</v>
+      </c>
+      <c r="G59" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H59" s="3" t="n">
+        <v>0.2032</v>
+      </c>
+      <c r="I59" s="3" t="n">
+        <v>5.17</v>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>Est. 12 cantos</t>
+        </is>
+      </c>
+      <c r="K59" s="3" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="L59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>06/11/2026 20:00</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>PD</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>Sevilla FC vs Deportivo Alavés</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>77.73717131249929</v>
+      </c>
+      <c r="G60" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H60" s="3" t="n">
+        <v>0.0883</v>
+      </c>
+      <c r="I60" s="3" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>Est. 10 cantos</t>
+        </is>
+      </c>
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="L60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
         <is>
           <t>PENDENTE</t>
         </is>
